--- a/research/traditional_assets/database/data/bahamas/bahamas_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_drugs_biotechnology.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-11.8</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
-        <v>0.02849364791288566</v>
+        <v>0.09152542372881356</v>
       </c>
       <c r="W2">
-        <v>-3.072916666666667</v>
+        <v>-5.09493670886076</v>
       </c>
       <c r="X2">
-        <v>0.09893434468750428</v>
+        <v>0.2130896874278793</v>
       </c>
       <c r="Y2">
-        <v>-3.171851011354171</v>
-      </c>
-      <c r="Z2">
-        <v>-0</v>
-      </c>
-      <c r="AA2">
-        <v>10.73928368893382</v>
+        <v>-5.308026396288639</v>
       </c>
       <c r="AB2">
-        <v>0.09864359875306929</v>
-      </c>
-      <c r="AC2">
-        <v>10.64064009018075</v>
+        <v>0.2116114939237332</v>
       </c>
       <c r="AD2">
-        <v>0.445</v>
+        <v>0.227</v>
       </c>
       <c r="AE2">
-        <v>0.3549674782284846</v>
+        <v>0.219180738760529</v>
       </c>
       <c r="AF2">
-        <v>0.7999674782284847</v>
+        <v>0.446180738760529</v>
       </c>
       <c r="AG2">
-        <v>-2.340032521771516</v>
+        <v>-2.253819261239471</v>
       </c>
       <c r="AH2">
-        <v>0.007206916329821359</v>
+        <v>0.0148994204854651</v>
       </c>
       <c r="AI2">
-        <v>0.3361253821938507</v>
+        <v>0.3659676736807172</v>
       </c>
       <c r="AJ2">
-        <v>-0.02169509760184056</v>
+        <v>-0.08272055752875405</v>
       </c>
       <c r="AK2">
-        <v>3.078858410318114</v>
+        <v>1.522008337028913</v>
       </c>
       <c r="AL2">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="AM2">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="AN2">
-        <v>-0.03849480968858132</v>
+        <v>-0.02071167883211679</v>
       </c>
       <c r="AO2">
-        <v>-278.5714285714286</v>
+        <v>-252.2727272727273</v>
       </c>
       <c r="AP2">
-        <v>0.202424958630754</v>
+        <v>0.2056404435437474</v>
       </c>
       <c r="AQ2">
-        <v>-334.2857142857142</v>
+        <v>-308.3333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +689,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-11.8</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +713,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
-        <v>0.02849364791288566</v>
+        <v>0.09152542372881356</v>
       </c>
       <c r="W3">
-        <v>-3.072916666666667</v>
+        <v>-5.09493670886076</v>
       </c>
       <c r="X3">
-        <v>0.09893434468750428</v>
+        <v>0.2130896874278793</v>
       </c>
       <c r="Y3">
-        <v>-3.171851011354171</v>
-      </c>
-      <c r="Z3">
-        <v>-0</v>
-      </c>
-      <c r="AA3">
-        <v>10.73928368893382</v>
+        <v>-5.308026396288639</v>
       </c>
       <c r="AB3">
-        <v>0.09864359875306929</v>
-      </c>
-      <c r="AC3">
-        <v>10.64064009018075</v>
+        <v>0.2116114939237332</v>
       </c>
       <c r="AD3">
-        <v>0.445</v>
+        <v>0.227</v>
       </c>
       <c r="AE3">
-        <v>0.3549674782284846</v>
+        <v>0.219180738760529</v>
       </c>
       <c r="AF3">
-        <v>0.7999674782284847</v>
+        <v>0.446180738760529</v>
       </c>
       <c r="AG3">
-        <v>-2.340032521771516</v>
+        <v>-2.253819261239471</v>
       </c>
       <c r="AH3">
-        <v>0.007206916329821359</v>
+        <v>0.0148994204854651</v>
       </c>
       <c r="AI3">
-        <v>0.3361253821938507</v>
+        <v>0.3659676736807172</v>
       </c>
       <c r="AJ3">
-        <v>-0.02169509760184056</v>
+        <v>-0.08272055752875405</v>
       </c>
       <c r="AK3">
-        <v>3.078858410318114</v>
+        <v>1.522008337028913</v>
       </c>
       <c r="AL3">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="AM3">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="AN3">
-        <v>-0.03849480968858132</v>
+        <v>-0.02071167883211679</v>
       </c>
       <c r="AO3">
-        <v>-278.5714285714286</v>
+        <v>-252.2727272727273</v>
       </c>
       <c r="AP3">
-        <v>0.202424958630754</v>
+        <v>0.2056404435437474</v>
       </c>
       <c r="AQ3">
-        <v>-334.2857142857142</v>
+        <v>-308.3333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bahamas/bahamas_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_drugs_biotechnology.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-8.050000000000001</v>
+        <v>-4.87</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,64 +612,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>0.076</v>
       </c>
       <c r="V2">
-        <v>0.09152542372881356</v>
+        <v>0.001381818181818182</v>
       </c>
       <c r="W2">
-        <v>-5.09493670886076</v>
+        <v>-6.30012936610608</v>
       </c>
       <c r="X2">
-        <v>0.2130896874278793</v>
+        <v>0.1675783658977514</v>
       </c>
       <c r="Y2">
-        <v>-5.308026396288639</v>
+        <v>-6.467707732003831</v>
       </c>
       <c r="AB2">
-        <v>0.2116114939237332</v>
+        <v>0.1674412893644966</v>
       </c>
       <c r="AD2">
-        <v>0.227</v>
+        <v>0.011</v>
       </c>
       <c r="AE2">
-        <v>0.219180738760529</v>
+        <v>0.1052092062125771</v>
       </c>
       <c r="AF2">
-        <v>0.446180738760529</v>
+        <v>0.1162092062125771</v>
       </c>
       <c r="AG2">
-        <v>-2.253819261239471</v>
+        <v>0.04020920621257708</v>
       </c>
       <c r="AH2">
-        <v>0.0148994204854651</v>
+        <v>0.002108439747330777</v>
       </c>
       <c r="AI2">
-        <v>0.3659676736807172</v>
+        <v>-0.065147329281724</v>
       </c>
       <c r="AJ2">
-        <v>-0.08272055752875405</v>
+        <v>0.0007305423942327335</v>
       </c>
       <c r="AK2">
-        <v>1.522008337028913</v>
+        <v>-0.02162028457549891</v>
       </c>
       <c r="AL2">
-        <v>0.044</v>
+        <v>0.06</v>
       </c>
       <c r="AM2">
-        <v>0.036</v>
+        <v>0.059</v>
       </c>
       <c r="AN2">
-        <v>-0.02071167883211679</v>
+        <v>-0.005901287553648069</v>
       </c>
       <c r="AO2">
-        <v>-252.2727272727273</v>
+        <v>-30.16666666666667</v>
       </c>
       <c r="AP2">
-        <v>0.2056404435437474</v>
+        <v>-0.02157146256039543</v>
       </c>
       <c r="AQ2">
-        <v>-308.3333333333334</v>
+        <v>-30.67796610169492</v>
       </c>
     </row>
     <row r="3">
@@ -680,7 +680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nymox Pharmaceutical Corporation (NasdaqCM:NYMX)</t>
+          <t>Nymox Pharmaceutical Corporation (OTCPK:NYMX.F)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-8.050000000000001</v>
+        <v>-4.87</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -713,64 +713,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.7</v>
+        <v>0.076</v>
       </c>
       <c r="V3">
-        <v>0.09152542372881356</v>
+        <v>0.001381818181818182</v>
       </c>
       <c r="W3">
-        <v>-5.09493670886076</v>
+        <v>-6.30012936610608</v>
       </c>
       <c r="X3">
-        <v>0.2130896874278793</v>
+        <v>0.1675783658977514</v>
       </c>
       <c r="Y3">
-        <v>-5.308026396288639</v>
+        <v>-6.467707732003831</v>
       </c>
       <c r="AB3">
-        <v>0.2116114939237332</v>
+        <v>0.1674412893644966</v>
       </c>
       <c r="AD3">
-        <v>0.227</v>
+        <v>0.011</v>
       </c>
       <c r="AE3">
-        <v>0.219180738760529</v>
+        <v>0.1052092062125771</v>
       </c>
       <c r="AF3">
-        <v>0.446180738760529</v>
+        <v>0.1162092062125771</v>
       </c>
       <c r="AG3">
-        <v>-2.253819261239471</v>
+        <v>0.04020920621257708</v>
       </c>
       <c r="AH3">
-        <v>0.0148994204854651</v>
+        <v>0.002108439747330777</v>
       </c>
       <c r="AI3">
-        <v>0.3659676736807172</v>
+        <v>-0.065147329281724</v>
       </c>
       <c r="AJ3">
-        <v>-0.08272055752875405</v>
+        <v>0.0007305423942327335</v>
       </c>
       <c r="AK3">
-        <v>1.522008337028913</v>
+        <v>-0.02162028457549891</v>
       </c>
       <c r="AL3">
-        <v>0.044</v>
+        <v>0.06</v>
       </c>
       <c r="AM3">
-        <v>0.036</v>
+        <v>0.059</v>
       </c>
       <c r="AN3">
-        <v>-0.02071167883211679</v>
+        <v>-0.005901287553648069</v>
       </c>
       <c r="AO3">
-        <v>-252.2727272727273</v>
+        <v>-30.16666666666667</v>
       </c>
       <c r="AP3">
-        <v>0.2056404435437474</v>
+        <v>-0.02157146256039543</v>
       </c>
       <c r="AQ3">
-        <v>-308.3333333333334</v>
+        <v>-30.67796610169492</v>
       </c>
     </row>
   </sheetData>
